--- a/survey_templates/035_pickleball_survey--survey_templates.xlsx
+++ b/survey_templates/035_pickleball_survey--survey_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -441,8 +441,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="21" customWidth="1" min="2" max="2"/>
-    <col width="21" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
     <col width="6" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>playing_style</t>
+          <t>playing_style_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Playing Style</t>
+          <t>Playing Style 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>practice_time</t>
+          <t>practice_time_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Practice Time</t>
+          <t>Practice Time 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>practice_frequency</t>
+          <t>practice_frequency_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Practice Frequency</t>
+          <t>Practice Frequency 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,12 +980,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>playing_level</t>
+          <t>playing_level_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Playing Level</t>
+          <t>Playing Level 2</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>frequency_played</t>
+          <t>frequency_played_2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Frequency Played</t>
+          <t>Frequency Played 2</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C85"/>
+  <dimension ref="A1:C78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
+    <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1284,29 +1284,29 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>hard_court</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hard Court</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>favorite_surface_choices</t>
+          <t>favorite_brand_choices</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>onnits</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Onnits</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>onnits</t>
+          <t>prince</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Onnits</t>
+          <t>Prince</t>
         </is>
       </c>
     </row>
@@ -1335,148 +1335,148 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>prince</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>favorite_brand_choices</t>
+          <t>playing_partners_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>prince</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>favorite_brand_choices</t>
+          <t>playing_partners_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>prince</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>favorite_brand_choices</t>
+          <t>playing_partners_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>prince</t>
+          <t>friend_and_family</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Prince</t>
+          <t>Friend And Family</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>favorite_brand_choices</t>
+          <t>playing_partners_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>alone</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Alone</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>playing_partners_choices</t>
+          <t>playing_style_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>friend</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Friend</t>
+          <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>playing_partners_choices</t>
+          <t>playing_style_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Family</t>
+          <t>Defend</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>playing_partners_choices</t>
+          <t>playing_style_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>friend_and_family</t>
+          <t>serve</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Friend And Family</t>
+          <t>Serve</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>playing_partners_choices</t>
+          <t>playing_style_choices</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>alone</t>
+          <t>return</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Alone</t>
+          <t>Return</t>
         </is>
       </c>
     </row>
@@ -1488,80 +1488,80 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>net</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Aggressive</t>
+          <t>Net</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>playing_level_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Defend</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>playing_level_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>serve</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Serve</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>playing_level_choices</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>return</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>playing_level_choices</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>net</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
@@ -1573,80 +1573,80 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>practice_frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>practice_frequency_choices</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>practice_frequency_choices</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Expert</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>practice_frequency_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1658,894 +1658,775 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>favorite_position_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>left</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Left</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>favorite_position_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>right</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Right</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>favorite_position_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>center</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Center</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>favorite_position_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>back</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Back</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>favorite_position_choices</t>
+          <t>playing_style_2_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>left</t>
+          <t>aggressive</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Left</t>
+          <t>Aggressive</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>favorite_position_choices</t>
+          <t>playing_style_2_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>right</t>
+          <t>defend</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Right</t>
+          <t>Defend</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>favorite_position_choices</t>
+          <t>playing_style_2_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>center</t>
+          <t>serve</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Center</t>
+          <t>Serve</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>favorite_position_choices</t>
+          <t>playing_style_2_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>back</t>
+          <t>return</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Back</t>
+          <t>Return</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>playing_style_2_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>aggressive</t>
+          <t>net</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Aggressive</t>
+          <t>Net</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>favorite_shot_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>defend</t>
+          <t>forehand</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Defend</t>
+          <t>Forehand</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>favorite_shot_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>serve</t>
+          <t>backhand</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Serve</t>
+          <t>Backhand</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>favorite_shot_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>return</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>playing_style_choices</t>
+          <t>practice_style_choices</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>net</t>
+          <t>alone</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Net</t>
+          <t>Alone</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>favorite_shot_choices</t>
+          <t>practice_style_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>forehand</t>
+          <t>with_a_partner</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Forehand</t>
+          <t>With A Partner</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>favorite_shot_choices</t>
+          <t>practice_style_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>backhand</t>
+          <t>with_a_coach</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Backhand</t>
+          <t>With A Coach</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>favorite_shot_choices</t>
+          <t>practice_style_choices</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>forehand</t>
+          <t>group_lesson</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Forehand</t>
+          <t>Group Lesson</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>favorite_shot_choices</t>
+          <t>practice_frequency_2_choices</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>backhand</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Backhand</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>favorite_shot_choices</t>
+          <t>practice_frequency_2_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>forehand</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Forehand</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>favorite_shot_choices</t>
+          <t>practice_frequency_2_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>practice_style_choices</t>
+          <t>practice_frequency_2_choices</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>alone</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Alone</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>practice_style_choices</t>
+          <t>practice_frequency_2_choices</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>with_a_partner</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>With A Partner</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>practice_style_choices</t>
+          <t>playing_level_2_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>with_a_coach</t>
+          <t>beginner</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>With A Coach</t>
+          <t>Beginner</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>practice_style_choices</t>
+          <t>playing_level_2_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>group_lesson</t>
+          <t>intermediate</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Group Lesson</t>
+          <t>Intermediate</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>playing_level_2_choices</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>advanced</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Advanced</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>playing_level_2_choices</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>expert</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Weekly</t>
+          <t>Expert</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>playing_level_2_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>occasionally</t>
+          <t>master</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Occasionally</t>
+          <t>Master</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>favorite_tournament_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>pro_tour</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Pro Tour</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>practice_frequency_choices</t>
+          <t>favorite_tournament_choices</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>never</t>
+          <t>amateur_tour</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Never</t>
+          <t>Amateur Tour</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>favorite_tournament_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>beginner</t>
+          <t>local_tour</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Beginner</t>
+          <t>Local Tour</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>favorite_tournament_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>intermediate</t>
+          <t>national_tour</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Intermediate</t>
+          <t>National Tour</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>favorite_tournament_choices</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>advanced</t>
+          <t>international_tour</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Advanced</t>
+          <t>International Tour</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>practice_place_choices</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>expert</t>
+          <t>home</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Expert</t>
+          <t>Home</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>playing_level_choices</t>
+          <t>practice_place_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>master</t>
+          <t>club</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Master</t>
+          <t>Club</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>favorite_tournament_choices</t>
+          <t>practice_place_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>pro_tour</t>
+          <t>gym</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Pro Tour</t>
+          <t>Gym</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>favorite_tournament_choices</t>
+          <t>practice_place_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>amateur_tour</t>
+          <t>park</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Amateur Tour</t>
+          <t>Park</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>favorite_tournament_choices</t>
+          <t>practice_place_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>local_tour</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Local Tour</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>favorite_tournament_choices</t>
+          <t>frequency_played_2_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>national_tour</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>National Tour</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>favorite_tournament_choices</t>
+          <t>frequency_played_2_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>international_tour</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>International Tour</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>practice_place_choices</t>
+          <t>frequency_played_2_choices</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>home</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Home</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>practice_place_choices</t>
+          <t>frequency_played_2_choices</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>club</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Club</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>practice_place_choices</t>
+          <t>frequency_played_2_choices</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>gym</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Gym</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>practice_place_choices</t>
+          <t>playing_partner_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>park</t>
+          <t>friend</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Park</t>
+          <t>Friend</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>practice_place_choices</t>
+          <t>playing_partner_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>family</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Other</t>
+          <t>Family</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>frequency_played_choices</t>
+          <t>playing_partner_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>friend_and_family</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Friend And Family</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>frequency_played_choices</t>
+          <t>playing_partner_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>weekly</t>
+          <t>alone</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
-        <is>
-          <t>Weekly</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>frequency_played_choices</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>occasionally</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Occasionally</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>frequency_played_choices</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>rarely</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Rarely</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>frequency_played_choices</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>never</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>Never</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>playing_partner_choices</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>friend</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>Friend</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>playing_partner_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>family</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Family</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>playing_partner_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>friend_and_family</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Friend And Family</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>playing_partner_choices</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>alone</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
         <is>
           <t>Alone</t>
         </is>
